--- a/output/yearly_total_coral_cover_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_33_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.295726755300106</v>
+        <v>1.26157175266936</v>
       </c>
       <c r="C3" t="n">
-        <v>4.63884320567661</v>
+        <v>4.576629853658489</v>
       </c>
       <c r="D3" t="n">
-        <v>6.100418339753119</v>
+        <v>6.089825282024296</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03498830072984</v>
+        <v>11.92802688835214</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.487820510753581</v>
+        <v>1.399432490587826</v>
       </c>
       <c r="C4" t="n">
-        <v>5.146828277025857</v>
+        <v>4.999789871740308</v>
       </c>
       <c r="D4" t="n">
-        <v>6.368896100712248</v>
+        <v>6.29601331121975</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00354488849169</v>
+        <v>12.69523567354788</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.734711475427043</v>
+        <v>1.599447492525862</v>
       </c>
       <c r="C5" t="n">
-        <v>5.772498005484914</v>
+        <v>5.519907304522134</v>
       </c>
       <c r="D5" t="n">
-        <v>6.653828155468445</v>
+        <v>6.594733916849698</v>
       </c>
       <c r="E5" t="n">
-        <v>14.1610376363804</v>
+        <v>13.71408871389769</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.013605300185974</v>
+        <v>1.831684914731923</v>
       </c>
       <c r="C6" t="n">
-        <v>6.519999789517883</v>
+        <v>6.152847985813924</v>
       </c>
       <c r="D6" t="n">
-        <v>7.096107139682492</v>
+        <v>6.888734831043796</v>
       </c>
       <c r="E6" t="n">
-        <v>15.62971222938635</v>
+        <v>14.87326773158964</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.322663785022086</v>
+        <v>2.115796443087914</v>
       </c>
       <c r="C7" t="n">
-        <v>7.35594097085259</v>
+        <v>6.940319568915243</v>
       </c>
       <c r="D7" t="n">
-        <v>7.531744517145156</v>
+        <v>7.228851000726734</v>
       </c>
       <c r="E7" t="n">
-        <v>17.21034927301983</v>
+        <v>16.28496701272989</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.495166217142452</v>
+        <v>1.365482932202433</v>
       </c>
       <c r="C8" t="n">
-        <v>4.927304477237642</v>
+        <v>4.668735754022258</v>
       </c>
       <c r="D8" t="n">
-        <v>5.871139538841494</v>
+        <v>5.42085211203634</v>
       </c>
       <c r="E8" t="n">
-        <v>12.29361023322159</v>
+        <v>11.45507079826103</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.916370170906874</v>
+        <v>1.757208274007103</v>
       </c>
       <c r="C9" t="n">
-        <v>5.92303173637176</v>
+        <v>5.770150988199038</v>
       </c>
       <c r="D9" t="n">
-        <v>6.448606330138738</v>
+        <v>5.833422576029371</v>
       </c>
       <c r="E9" t="n">
-        <v>14.28800823741737</v>
+        <v>13.36078183823551</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.369815118509106</v>
+        <v>2.164715634437917</v>
       </c>
       <c r="C10" t="n">
-        <v>7.022489795292817</v>
+        <v>7.052606169261215</v>
       </c>
       <c r="D10" t="n">
-        <v>7.07202412892803</v>
+        <v>6.249414402635365</v>
       </c>
       <c r="E10" t="n">
-        <v>16.46432904272995</v>
+        <v>15.4667362063345</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.849556815335585</v>
+        <v>2.585926583692415</v>
       </c>
       <c r="C11" t="n">
-        <v>8.171930327979355</v>
+        <v>8.505587084157959</v>
       </c>
       <c r="D11" t="n">
-        <v>7.667758563283996</v>
+        <v>6.748284441003336</v>
       </c>
       <c r="E11" t="n">
-        <v>18.68924570659894</v>
+        <v>17.83979810885371</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.334376988704657</v>
+        <v>3.014193883797598</v>
       </c>
       <c r="C12" t="n">
-        <v>9.396122424340048</v>
+        <v>10.07326362876089</v>
       </c>
       <c r="D12" t="n">
-        <v>8.231080327573263</v>
+        <v>7.184420715066747</v>
       </c>
       <c r="E12" t="n">
-        <v>20.96157974061797</v>
+        <v>20.27187822762523</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.810528743477998</v>
+        <v>3.432010698034503</v>
       </c>
       <c r="C13" t="n">
-        <v>10.69041646688678</v>
+        <v>11.7258062284934</v>
       </c>
       <c r="D13" t="n">
-        <v>8.77734566868742</v>
+        <v>7.608006133453791</v>
       </c>
       <c r="E13" t="n">
-        <v>23.2782908790522</v>
+        <v>22.7658230599817</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.181953907642621</v>
+        <v>1.976189406309532</v>
       </c>
       <c r="C14" t="n">
-        <v>7.621523412562922</v>
+        <v>8.216010917392536</v>
       </c>
       <c r="D14" t="n">
-        <v>6.669002337471541</v>
+        <v>5.803081227371769</v>
       </c>
       <c r="E14" t="n">
-        <v>16.47247965767708</v>
+        <v>15.99528155107384</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.279794883847858</v>
+        <v>2.044587768864408</v>
       </c>
       <c r="C15" t="n">
-        <v>8.110973730515171</v>
+        <v>9.03301153938969</v>
       </c>
       <c r="D15" t="n">
-        <v>6.751920748572227</v>
+        <v>5.782945581957668</v>
       </c>
       <c r="E15" t="n">
-        <v>17.14268936293526</v>
+        <v>16.86054489021177</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.697057293106838</v>
+        <v>2.398694348309189</v>
       </c>
       <c r="C16" t="n">
-        <v>9.540908896704735</v>
+        <v>10.81739689672052</v>
       </c>
       <c r="D16" t="n">
-        <v>7.308925126053697</v>
+        <v>6.21458077760682</v>
       </c>
       <c r="E16" t="n">
-        <v>19.54689131586527</v>
+        <v>19.43067202263653</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.196081257106733</v>
+        <v>1.938097595384756</v>
       </c>
       <c r="C17" t="n">
-        <v>8.797244828214819</v>
+        <v>10.14133597514504</v>
       </c>
       <c r="D17" t="n">
-        <v>6.829292285143917</v>
+        <v>5.727938258088718</v>
       </c>
       <c r="E17" t="n">
-        <v>17.82261837046547</v>
+        <v>17.80737182861852</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.537169861993202</v>
+        <v>2.229647211114931</v>
       </c>
       <c r="C18" t="n">
-        <v>10.26537979757663</v>
+        <v>11.93675617667161</v>
       </c>
       <c r="D18" t="n">
-        <v>7.335952640351611</v>
+        <v>6.079443206117246</v>
       </c>
       <c r="E18" t="n">
-        <v>20.13850229992144</v>
+        <v>20.24584659390379</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.577264438234642</v>
+        <v>2.248781473870701</v>
       </c>
       <c r="C19" t="n">
-        <v>10.99027284996134</v>
+        <v>12.85612363179058</v>
       </c>
       <c r="D19" t="n">
-        <v>7.495290292750868</v>
+        <v>6.147851386149163</v>
       </c>
       <c r="E19" t="n">
-        <v>21.06282758094685</v>
+        <v>21.25275649181044</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.905492148195478</v>
+        <v>2.512783249019711</v>
       </c>
       <c r="C20" t="n">
-        <v>12.61787309892396</v>
+        <v>14.79803040826781</v>
       </c>
       <c r="D20" t="n">
-        <v>7.989138840418142</v>
+        <v>6.492523370156134</v>
       </c>
       <c r="E20" t="n">
-        <v>23.51250408753758</v>
+        <v>23.80333702744366</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.745056544298706</v>
+        <v>1.501111874747458</v>
       </c>
       <c r="C21" t="n">
-        <v>9.342320971089691</v>
+        <v>10.84260817776558</v>
       </c>
       <c r="D21" t="n">
-        <v>6.692593734804592</v>
+        <v>5.385318126783624</v>
       </c>
       <c r="E21" t="n">
-        <v>17.77997125019299</v>
+        <v>17.72903817929667</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_33_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26157175266936</v>
+        <v>1.265793267797621</v>
       </c>
       <c r="C3" t="n">
-        <v>4.576629853658489</v>
+        <v>4.644164278233627</v>
       </c>
       <c r="D3" t="n">
-        <v>6.089825282024296</v>
+        <v>6.073999509031837</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92802688835214</v>
+        <v>11.98395705506308</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.399432490587826</v>
+        <v>1.412244504332146</v>
       </c>
       <c r="C4" t="n">
-        <v>4.999789871740308</v>
+        <v>5.160638185147565</v>
       </c>
       <c r="D4" t="n">
-        <v>6.29601331121975</v>
+        <v>6.283848326426114</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69523567354788</v>
+        <v>12.85673101590583</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.599447492525862</v>
+        <v>1.609026758307015</v>
       </c>
       <c r="C5" t="n">
-        <v>5.519907304522134</v>
+        <v>5.805273984829348</v>
       </c>
       <c r="D5" t="n">
-        <v>6.594733916849698</v>
+        <v>6.614841114315935</v>
       </c>
       <c r="E5" t="n">
-        <v>13.71408871389769</v>
+        <v>14.0291418574523</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.831684914731923</v>
+        <v>1.82215266525652</v>
       </c>
       <c r="C6" t="n">
-        <v>6.152847985813924</v>
+        <v>6.565213668751298</v>
       </c>
       <c r="D6" t="n">
-        <v>6.888734831043796</v>
+        <v>6.939527668238264</v>
       </c>
       <c r="E6" t="n">
-        <v>14.87326773158964</v>
+        <v>15.32689400224608</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.115796443087914</v>
+        <v>2.070222053518546</v>
       </c>
       <c r="C7" t="n">
-        <v>6.940319568915243</v>
+        <v>7.420736788516054</v>
       </c>
       <c r="D7" t="n">
-        <v>7.228851000726734</v>
+        <v>7.260168119677642</v>
       </c>
       <c r="E7" t="n">
-        <v>16.28496701272989</v>
+        <v>16.75112696171224</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.365482932202433</v>
+        <v>1.290675436483596</v>
       </c>
       <c r="C8" t="n">
-        <v>4.668735754022258</v>
+        <v>5.052479922081065</v>
       </c>
       <c r="D8" t="n">
-        <v>5.42085211203634</v>
+        <v>5.43951639540265</v>
       </c>
       <c r="E8" t="n">
-        <v>11.45507079826103</v>
+        <v>11.78267175396731</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.757208274007103</v>
+        <v>1.63200390453083</v>
       </c>
       <c r="C9" t="n">
-        <v>5.770150988199038</v>
+        <v>6.195304004167754</v>
       </c>
       <c r="D9" t="n">
-        <v>5.833422576029371</v>
+        <v>5.898695929540644</v>
       </c>
       <c r="E9" t="n">
-        <v>13.36078183823551</v>
+        <v>13.72600383823923</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.164715634437917</v>
+        <v>1.985901946280648</v>
       </c>
       <c r="C10" t="n">
-        <v>7.052606169261215</v>
+        <v>7.576365863995493</v>
       </c>
       <c r="D10" t="n">
-        <v>6.249414402635365</v>
+        <v>6.388686970654065</v>
       </c>
       <c r="E10" t="n">
-        <v>15.4667362063345</v>
+        <v>15.95095478093021</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.585926583692415</v>
+        <v>2.340751944218701</v>
       </c>
       <c r="C11" t="n">
-        <v>8.505587084157959</v>
+        <v>9.126573872558588</v>
       </c>
       <c r="D11" t="n">
-        <v>6.748284441003336</v>
+        <v>6.904380419709532</v>
       </c>
       <c r="E11" t="n">
-        <v>17.83979810885371</v>
+        <v>18.37170623648682</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.014193883797598</v>
+        <v>2.696353511155215</v>
       </c>
       <c r="C12" t="n">
-        <v>10.07326362876089</v>
+        <v>10.80172892659323</v>
       </c>
       <c r="D12" t="n">
-        <v>7.184420715066747</v>
+        <v>7.352898996851944</v>
       </c>
       <c r="E12" t="n">
-        <v>20.27187822762523</v>
+        <v>20.85098143460039</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.432010698034503</v>
+        <v>3.03903866485801</v>
       </c>
       <c r="C13" t="n">
-        <v>11.7258062284934</v>
+        <v>12.52282398428537</v>
       </c>
       <c r="D13" t="n">
-        <v>7.608006133453791</v>
+        <v>7.825324788296178</v>
       </c>
       <c r="E13" t="n">
-        <v>22.7658230599817</v>
+        <v>23.38718743743956</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.976189406309532</v>
+        <v>1.754108258131861</v>
       </c>
       <c r="C14" t="n">
-        <v>8.216010917392536</v>
+        <v>8.794525387074055</v>
       </c>
       <c r="D14" t="n">
-        <v>5.803081227371769</v>
+        <v>5.956135694463846</v>
       </c>
       <c r="E14" t="n">
-        <v>15.99528155107384</v>
+        <v>16.50476933966976</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.044587768864408</v>
+        <v>1.792229521487765</v>
       </c>
       <c r="C15" t="n">
-        <v>9.03301153938969</v>
+        <v>9.611260937191062</v>
       </c>
       <c r="D15" t="n">
-        <v>5.782945581957668</v>
+        <v>5.962428697248068</v>
       </c>
       <c r="E15" t="n">
-        <v>16.86054489021177</v>
+        <v>17.3659191559269</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.398694348309189</v>
+        <v>2.084672527628805</v>
       </c>
       <c r="C16" t="n">
-        <v>10.81739689672052</v>
+        <v>11.45813453589721</v>
       </c>
       <c r="D16" t="n">
-        <v>6.21458077760682</v>
+        <v>6.41215750308649</v>
       </c>
       <c r="E16" t="n">
-        <v>19.43067202263653</v>
+        <v>19.9549645666125</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.938097595384756</v>
+        <v>1.672927540467693</v>
       </c>
       <c r="C17" t="n">
-        <v>10.14133597514504</v>
+        <v>10.65463294483344</v>
       </c>
       <c r="D17" t="n">
-        <v>5.727938258088718</v>
+        <v>5.936795264690184</v>
       </c>
       <c r="E17" t="n">
-        <v>17.80737182861852</v>
+        <v>18.26435574999132</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.229647211114931</v>
+        <v>1.911060263609799</v>
       </c>
       <c r="C18" t="n">
-        <v>11.93675617667161</v>
+        <v>12.53434600424664</v>
       </c>
       <c r="D18" t="n">
-        <v>6.079443206117246</v>
+        <v>6.307611190061248</v>
       </c>
       <c r="E18" t="n">
-        <v>20.24584659390379</v>
+        <v>20.75301745791769</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.248781473870701</v>
+        <v>1.914250943648601</v>
       </c>
       <c r="C19" t="n">
-        <v>12.85612363179058</v>
+        <v>13.50025811802395</v>
       </c>
       <c r="D19" t="n">
-        <v>6.147851386149163</v>
+        <v>6.378640636463503</v>
       </c>
       <c r="E19" t="n">
-        <v>21.25275649181044</v>
+        <v>21.79314969813606</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.512783249019711</v>
+        <v>2.124335134880376</v>
       </c>
       <c r="C20" t="n">
-        <v>14.79803040826781</v>
+        <v>15.56928158724706</v>
       </c>
       <c r="D20" t="n">
-        <v>6.492523370156134</v>
+        <v>6.78769563491498</v>
       </c>
       <c r="E20" t="n">
-        <v>23.80333702744366</v>
+        <v>24.48131235704242</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.501111874747458</v>
+        <v>1.261241458168835</v>
       </c>
       <c r="C21" t="n">
-        <v>10.84260817776558</v>
+        <v>11.46787347312334</v>
       </c>
       <c r="D21" t="n">
-        <v>5.385318126783624</v>
+        <v>5.653757401555829</v>
       </c>
       <c r="E21" t="n">
-        <v>17.72903817929667</v>
+        <v>18.382872332848</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_33_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.265793267797621</v>
+        <v>2.620843740709687</v>
       </c>
       <c r="C3" t="n">
-        <v>4.644164278233627</v>
+        <v>7.684892396228561</v>
       </c>
       <c r="D3" t="n">
-        <v>6.073999509031837</v>
+        <v>8.122615063344959</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98395705506308</v>
+        <v>18.42835120028321</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.412244504332146</v>
+        <v>1.129783354934768</v>
       </c>
       <c r="C4" t="n">
-        <v>5.160638185147565</v>
+        <v>4.429675514204902</v>
       </c>
       <c r="D4" t="n">
-        <v>6.283848326426114</v>
+        <v>5.680058938008709</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85673101590583</v>
+        <v>11.23951780714838</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.609026758307015</v>
+        <v>1.273455664440787</v>
       </c>
       <c r="C5" t="n">
-        <v>5.805273984829348</v>
+        <v>5.005716051942831</v>
       </c>
       <c r="D5" t="n">
-        <v>6.614841114315935</v>
+        <v>5.960961421983205</v>
       </c>
       <c r="E5" t="n">
-        <v>14.0291418574523</v>
+        <v>12.24013313836682</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.82215266525652</v>
+        <v>1.42426558579165</v>
       </c>
       <c r="C6" t="n">
-        <v>6.565213668751298</v>
+        <v>5.717775607268914</v>
       </c>
       <c r="D6" t="n">
-        <v>6.939527668238264</v>
+        <v>6.309312070057873</v>
       </c>
       <c r="E6" t="n">
-        <v>15.32689400224608</v>
+        <v>13.45135326311844</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.070222053518546</v>
+        <v>1.569591929022255</v>
       </c>
       <c r="C7" t="n">
-        <v>7.420736788516054</v>
+        <v>6.559070635029906</v>
       </c>
       <c r="D7" t="n">
-        <v>7.260168119677642</v>
+        <v>6.635357990496334</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75112696171224</v>
+        <v>14.76402055454849</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.290675436483596</v>
+        <v>1.723352491844648</v>
       </c>
       <c r="C8" t="n">
-        <v>5.052479922081065</v>
+        <v>7.573133739888664</v>
       </c>
       <c r="D8" t="n">
-        <v>5.43951639540265</v>
+        <v>7.104940639756265</v>
       </c>
       <c r="E8" t="n">
-        <v>11.78267175396731</v>
+        <v>16.40142687148958</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.63200390453083</v>
+        <v>1.873895492986121</v>
       </c>
       <c r="C9" t="n">
-        <v>6.195304004167754</v>
+        <v>8.750140570888572</v>
       </c>
       <c r="D9" t="n">
-        <v>5.898695929540644</v>
+        <v>7.540097054750002</v>
       </c>
       <c r="E9" t="n">
-        <v>13.72600383823923</v>
+        <v>18.16413311862469</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.985901946280648</v>
+        <v>1.158187401654047</v>
       </c>
       <c r="C10" t="n">
-        <v>7.576365863995493</v>
+        <v>6.575971925017113</v>
       </c>
       <c r="D10" t="n">
-        <v>6.388686970654065</v>
+        <v>5.971637490713904</v>
       </c>
       <c r="E10" t="n">
-        <v>15.95095478093021</v>
+        <v>13.70579681738506</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.340751944218701</v>
+        <v>1.09022100808904</v>
       </c>
       <c r="C11" t="n">
-        <v>9.126573872558588</v>
+        <v>7.00873613052615</v>
       </c>
       <c r="D11" t="n">
-        <v>6.904380419709532</v>
+        <v>5.850892340568588</v>
       </c>
       <c r="E11" t="n">
-        <v>18.37170623648682</v>
+        <v>13.94984947918378</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.696353511155215</v>
+        <v>1.180708693989469</v>
       </c>
       <c r="C12" t="n">
-        <v>10.80172892659323</v>
+        <v>8.347349125266675</v>
       </c>
       <c r="D12" t="n">
-        <v>7.352898996851944</v>
+        <v>6.246948999415837</v>
       </c>
       <c r="E12" t="n">
-        <v>20.85098143460039</v>
+        <v>15.77500681867198</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.03903866485801</v>
+        <v>0.9297837982610269</v>
       </c>
       <c r="C13" t="n">
-        <v>12.52282398428537</v>
+        <v>8.021349982594481</v>
       </c>
       <c r="D13" t="n">
-        <v>7.825324788296178</v>
+        <v>5.728988728132262</v>
       </c>
       <c r="E13" t="n">
-        <v>23.38718743743956</v>
+        <v>14.68012250898777</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.754108258131861</v>
+        <v>1.014734427109503</v>
       </c>
       <c r="C14" t="n">
-        <v>8.794525387074055</v>
+        <v>9.466413880906487</v>
       </c>
       <c r="D14" t="n">
-        <v>5.956135694463846</v>
+        <v>6.104507225006667</v>
       </c>
       <c r="E14" t="n">
-        <v>16.50476933966976</v>
+        <v>16.58565553302266</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.792229521487765</v>
+        <v>0.9852132736428016</v>
       </c>
       <c r="C15" t="n">
-        <v>9.611260937191062</v>
+        <v>10.28434716322267</v>
       </c>
       <c r="D15" t="n">
-        <v>5.962428697248068</v>
+        <v>6.164973066111227</v>
       </c>
       <c r="E15" t="n">
-        <v>17.3659191559269</v>
+        <v>17.4345335029767</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.084672527628805</v>
+        <v>1.077163763622558</v>
       </c>
       <c r="C16" t="n">
-        <v>11.45813453589721</v>
+        <v>12.04473860666172</v>
       </c>
       <c r="D16" t="n">
-        <v>6.41215750308649</v>
+        <v>6.548846235948774</v>
       </c>
       <c r="E16" t="n">
-        <v>19.9549645666125</v>
+        <v>19.67074860623305</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.672927540467693</v>
+        <v>0.648856692690802</v>
       </c>
       <c r="C17" t="n">
-        <v>10.65463294483344</v>
+        <v>9.064221298907697</v>
       </c>
       <c r="D17" t="n">
-        <v>5.936795264690184</v>
+        <v>5.450692706409419</v>
       </c>
       <c r="E17" t="n">
-        <v>18.26435574999132</v>
+        <v>15.16377069800792</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.911060263609799</v>
+        <v>0.5041372636077797</v>
       </c>
       <c r="C18" t="n">
-        <v>12.53434600424664</v>
+        <v>8.100537752419028</v>
       </c>
       <c r="D18" t="n">
-        <v>6.307611190061248</v>
+        <v>4.959701044561505</v>
       </c>
       <c r="E18" t="n">
-        <v>20.75301745791769</v>
+        <v>13.56437606058831</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.914250943648601</v>
+        <v>0.5857892201699868</v>
       </c>
       <c r="C19" t="n">
-        <v>13.50025811802395</v>
+        <v>10.02258377283935</v>
       </c>
       <c r="D19" t="n">
-        <v>6.378640636463503</v>
+        <v>5.442995804408124</v>
       </c>
       <c r="E19" t="n">
-        <v>21.79314969813606</v>
+        <v>16.05136879741746</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.124335134880376</v>
+        <v>0.6632589315121027</v>
       </c>
       <c r="C20" t="n">
-        <v>15.56928158724706</v>
+        <v>12.0823002738262</v>
       </c>
       <c r="D20" t="n">
-        <v>6.78769563491498</v>
+        <v>5.888660174750963</v>
       </c>
       <c r="E20" t="n">
-        <v>24.48131235704242</v>
+        <v>18.63421938008926</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.261241458168835</v>
+        <v>0.729163654898191</v>
       </c>
       <c r="C21" t="n">
-        <v>11.46787347312334</v>
+        <v>14.14010236678977</v>
       </c>
       <c r="D21" t="n">
-        <v>5.653757401555829</v>
+        <v>6.345153222271645</v>
       </c>
       <c r="E21" t="n">
-        <v>18.382872332848</v>
+        <v>21.2144192439596</v>
       </c>
     </row>
   </sheetData>
